--- a/assessment_forms/033_semantic_knowledge_assessment--assessment_forms.xlsx
+++ b/assessment_forms/033_semantic_knowledge_assessment--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="43" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>semantic_knowledge_assessment</t>
+          <t>semantic_knowledge_definition</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>semantic_knowledge_assessment</t>
+          <t>What is the definition of semantic knowledge?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>evaluation_form</t>
+          <t>conceptual_learning_data</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>evaluation_form</t>
+          <t>How would you describe your experience with conceptual learning data?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>assessment_form</t>
+          <t>primary_users_of_semantic_knowledge</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>assessment_form</t>
+          <t>Who are the primary users of semantic knowledge?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>conceptual_learning_data</t>
+          <t>ideal_use_of_semantic_knowledge</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>conceptual_learning_data</t>
+          <t>What is the ideal use of semantic knowledge?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>educators_trainers_researchers</t>
+          <t>knowledge_types</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>educators_trainers_researchers</t>
+          <t>What types of knowledge are you interested in collecting?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>collecting_conceptual_data</t>
+          <t>collecting_semantic_knowledge</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>collecting_conceptual_data</t>
+          <t>How do you currently collect data on semantic knowledge?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ideal_use</t>
+          <t>benefits_of_semantic_knowledge</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ideal_use</t>
+          <t>What are the benefits of semantic knowledge?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>semantic_knowledge</t>
+          <t>limitations_of_semantic_knowledge</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>semantic_knowledge</t>
+          <t>What are the limitations of semantic knowledge?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>knowledge_types</t>
+          <t>applying_semantic_knowledge</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>knowledge_types</t>
+          <t>How do you apply semantic knowledge in your work or daily life?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>semantic_knowledge_assessment_form</t>
+          <t>example_of_semantic_knowledge</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>semantic_knowledge_assessment_form</t>
+          <t>Can you give an example of a situation where semantic knowledge was useful?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>mixed_question_types</t>
+          <t>characteristics_of_semantic_knowledge</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>mixed_question_types</t>
+          <t>What are the key characteristics of semantic knowledge?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ideal_for_educators</t>
+          <t>evaluating_semantic_knowledge</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ideal_for_educators</t>
+          <t>How do you evaluate the quality of semantic knowledge?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ideal_for_trainers</t>
+          <t>tools_for_semantic_knowledge</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ideal_for_trainers</t>
+          <t>What tools or resources do you use to collect and evaluate semantic knowledge?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ideal_for_researchers</t>
+          <t>challenges_with_semantic_knowledge</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ideal_for_researchers</t>
+          <t>What are the challenges you face when collecting and evaluating semantic knowledge?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>collecting_data_online</t>
+          <t>ideal_tools_for_semantic_knowledge</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>collecting_data_online</t>
+          <t>What are the ideal tools for semantic knowledge?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>form_evaluate</t>
+          <t>future_directions_for_semantic_knowledge</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>form_evaluate</t>
+          <t>What are the future directions for semantic knowledge research?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>relationship_with_other_areas</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>What is the relationship between semantic knowledge and other areas of research?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>form_version</t>
+          <t>integrating_semantic_knowledge</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>form_version</t>
+          <t>How can semantic knowledge be integrated into existing research?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>impact_on_education_and_training</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>How does semantic knowledge impact education and training?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>applying_semantic_knowledge_in_real_world</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>How can semantic knowledge be applied in real-world scenarios?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>category_id</t>
+          <t>benefits_and_limitations</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>category_id</t>
+          <t>What are the benefits and limitations of semantic knowledge?</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>evaluating_semantic_knowledge_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>How can semantic knowledge be evaluated?</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>features_of_semantic_knowledge</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>What are the key features of semantic knowledge?</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>form_version</t>
+          <t>improving_decision_making</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>form_version</t>
+          <t>How can semantic knowledge be used to improve decision-making?</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,16 +1072,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>implications_on_individual_and_society</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>What are the implications of semantic knowledge on individual and society?</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>future_research_directions</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>What are the future research directions for semantic knowledge?</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +1121,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,136 +1149,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>educators_trainers_researchers_choices</t>
+          <t>primary_users_of_semantic_knowledge_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'educators'}</t>
+          <t>educators</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'educators'}</t>
+          <t>educators</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>educators_trainers_researchers_choices</t>
+          <t>primary_users_of_semantic_knowledge_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'trainers'}</t>
+          <t>trainers</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'trainers'}</t>
+          <t>trainers</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>educators_trainers_researchers_choices</t>
+          <t>primary_users_of_semantic_knowledge_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'researchers'}</t>
+          <t>researchers</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'researchers'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>semantic_knowledge_assessment_form_choices</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>{'value':_'semantic_knowledge'}</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>{'value': 'semantic_knowledge'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>semantic_knowledge_assessment_form_choices</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>{'value':_'conceptual_learning'}</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>{'value': 'conceptual_learning'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>form_evaluate_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>{'value':_true}</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>{'value': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>form_evaluate_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{'value':_false}</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>{'value': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>form_evaluate_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>{'value':_none}</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>{'value': None}</t>
+          <t>researchers</t>
         </is>
       </c>
     </row>
